--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488041_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488041_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8292</v>
+        <v>5.0945</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2689</v>
+        <v>3.5622</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5604</v>
+        <v>1.5323</v>
       </c>
       <c r="G2" t="n">
         <v>2.7675</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1031</v>
+        <v>1.3683</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7844</v>
+        <v>1.0776</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3188</v>
+        <v>0.2907</v>
       </c>
       <c r="V2" t="n">
         <v>1.1568</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4872</v>
+        <v>4.3484</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3059</v>
+        <v>3.5109</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1813</v>
+        <v>0.8375</v>
       </c>
       <c r="G3" t="n">
-        <v>1.317</v>
+        <v>4.1772</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3701</v>
+        <v>0.5325</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9469</v>
+        <v>3.6448</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3972</v>
+        <v>4.4082</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2767</v>
+        <v>0.7806</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1205</v>
+        <v>3.6277</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9198</v>
+        <v>-0.231</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0934</v>
+        <v>-0.2481</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8264</v>
+        <v>0.0171</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7929</v>
+        <v>0.7929</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0838</v>
+        <v>0.0321</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4172</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6666</v>
+        <v>-0.0616</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1207</v>
+        <v>-0.6539</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5944</v>
+        <v>-0.6539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5466</v>
+        <v>1.8414</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2426</v>
+        <v>0.4744</v>
       </c>
       <c r="F4" t="n">
-        <v>0.304</v>
+        <v>1.367</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1772</v>
+        <v>1.317</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5325</v>
+        <v>0.3701</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6448</v>
+        <v>0.9469</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4082</v>
+        <v>0.3972</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7806</v>
+        <v>0.2767</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6277</v>
+        <v>0.1205</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.231</v>
+        <v>0.9198</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2481</v>
+        <v>0.0934</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0171</v>
+        <v>0.8264</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7929</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7696</v>
+        <v>1.438</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1745</v>
+        <v>0.5857</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5951</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6539</v>
+        <v>-0.1207</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6539</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7742</v>
+        <v>1.5224</v>
       </c>
       <c r="E5" t="n">
-        <v>0.713</v>
+        <v>-0.0098</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0612</v>
+        <v>1.5321</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8714</v>
+        <v>-0.5881</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8126</v>
+        <v>0.596</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9412</v>
+        <v>-1.1841</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6443</v>
+        <v>-0.8209</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9987</v>
+        <v>0.6462</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3544</v>
+        <v>-1.4671</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2271</v>
+        <v>0.2328</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1861</v>
+        <v>-0.0503</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4132</v>
+        <v>0.2831</v>
       </c>
       <c r="P5" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.9822</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>3.438</v>
+        <v>0.9646</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9142</v>
+        <v>0.6655</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5237</v>
+        <v>0.2991</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5441</v>
+        <v>0.7494</v>
       </c>
       <c r="W5" t="n">
         <v>1.1367</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.6808</v>
+        <v>-0.3873</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4015</v>
+        <v>0.9902</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3748</v>
+        <v>0.6965</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0267</v>
+        <v>0.2937</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5881</v>
+        <v>0.8714</v>
       </c>
       <c r="H6" t="n">
-        <v>0.596</v>
+        <v>1.8126</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1841</v>
+        <v>-0.9412</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8209</v>
+        <v>0.6443</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6462</v>
+        <v>1.9987</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4671</v>
+        <v>-1.3544</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2328</v>
+        <v>0.2271</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0503</v>
+        <v>-0.1861</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2831</v>
+        <v>0.4132</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3964</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8437</v>
+        <v>2.654</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0501</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2064</v>
+        <v>1.7563</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7494</v>
+        <v>-1.5441</v>
       </c>
       <c r="W6" t="n">
         <v>1.1367</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3873</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1823</v>
+        <v>0.5607</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4551</v>
+        <v>1.7212</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2728</v>
+        <v>-1.1605</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7343</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4867</v>
+        <v>-0.1082</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8184</v>
+        <v>-0.5523</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3317</v>
+        <v>0.444</v>
       </c>
       <c r="V7" t="n">
         <v>2.0068</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9402</v>
+        <v>-0.8217</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1046</v>
+        <v>-0.0422</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8356</v>
+        <v>-0.7795</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3096</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6307</v>
+        <v>-0.5121</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1248</v>
+        <v>-0.0624</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5059</v>
+        <v>-0.4497</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6949</v>
+        <v>-1.2946</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1019</v>
+        <v>-0.8982</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.593</v>
+        <v>-0.3965</v>
       </c>
       <c r="G9" t="n">
         <v>-1.514</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.181</v>
+        <v>0.2193</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.312</v>
+        <v>-0.1082</v>
       </c>
       <c r="U9" t="n">
-        <v>0.131</v>
+        <v>0.3276</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2646</v>
+        <v>-3.0483</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4596</v>
+        <v>-2.3556</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.805</v>
+        <v>-0.6927</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5676</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6467</v>
+        <v>-0.4304</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7471</v>
+        <v>-0.6431</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1004</v>
+        <v>0.2127</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6539</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7957</v>
+        <v>-5.2116</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8393</v>
+        <v>-2.9182</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9564</v>
+        <v>-2.2934</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4315</v>
@@ -1312,13 +1312,13 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2988</v>
+        <v>0.8829</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2351</v>
+        <v>0.1562</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0636</v>
+        <v>0.7267</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0772</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.525600000000001</v>
+        <v>3.9814</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8549</v>
+        <v>3.741200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6707999999999998</v>
+        <v>0.2400000000000007</v>
       </c>
       <c r="G12" t="n">
         <v>0.9880000000000004</v>
@@ -1360,10 +1360,10 @@
         <v>1.3741</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3861000000000003</v>
+        <v>-0.3860999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>8.0122</v>
+        <v>8.012199999999998</v>
       </c>
       <c r="K12" t="n">
         <v>10.2892</v>
@@ -1390,19 +1390,19 @@
         <v>11.497</v>
       </c>
       <c r="S12" t="n">
-        <v>6.0527</v>
+        <v>6.5085</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2242</v>
+        <v>2.1105</v>
       </c>
       <c r="U12" t="n">
-        <v>4.8284</v>
+        <v>4.398099999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1368</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4942</v>
+        <v>7.494200000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-8.631</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.6688</v>
+        <v>5.3504</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5824</v>
+        <v>5.1563</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0864</v>
+        <v>0.1941</v>
       </c>
       <c r="G13" t="n">
         <v>4.6437</v>
@@ -1468,13 +1468,13 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9745</v>
+        <v>0.6561</v>
       </c>
       <c r="T13" t="n">
-        <v>1.843</v>
+        <v>0.4168</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1316</v>
+        <v>0.2393</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6536</v>
+        <v>3.0713</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1595</v>
+        <v>0.7573</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8131</v>
+        <v>2.314</v>
       </c>
       <c r="G14" t="n">
         <v>1.7113</v>
@@ -1546,13 +1546,13 @@
         <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8526</v>
+        <v>-0.435</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3727</v>
+        <v>-0.4559</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4799</v>
+        <v>0.0209</v>
       </c>
       <c r="V14" t="n">
         <v>0.4074</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.608</v>
+        <v>1.211</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6208</v>
+        <v>2.1115</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0128</v>
+        <v>-0.9005</v>
       </c>
       <c r="G15" t="n">
         <v>0.3378</v>
@@ -1624,13 +1624,13 @@
         <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.384</v>
+        <v>-0.781</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0479</v>
+        <v>-0.4614</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4319</v>
+        <v>-0.3196</v>
       </c>
       <c r="V15" t="n">
         <v>0.2666</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>J. PÁEZ ÁVILA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8514</v>
+        <v>0.3027</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9746</v>
+        <v>0.3027</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1233</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8454</v>
+        <v>0.3027</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1669</v>
+        <v>0.3027</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.788</v>
+        <v>0.3027</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3085</v>
+        <v>0.3027</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0965</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6334</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8584</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.784</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3264</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6022999999999999</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2759</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.1545</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>5.5577</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PÁEZ ÁVILA</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3027</v>
+        <v>0.2891</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3027</v>
+        <v>3.1597</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-2.8706</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3027</v>
+        <v>-1.8454</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3027</v>
+        <v>-2.1669</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.3214</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3027</v>
+        <v>0.788</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3027</v>
+        <v>-0.3085</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.0965</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-2.6334</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.8584</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.775</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.784</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.2359</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.2127</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.0232</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.1545</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>5.5577</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4033</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2098</v>
+        <v>0.0472</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2121</v>
+        <v>-1.314</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4219</v>
+        <v>1.3611</v>
       </c>
       <c r="G18" t="n">
         <v>-0.07820000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0907</v>
+        <v>-0.2533</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6312</v>
+        <v>-0.7331</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5405</v>
+        <v>0.4798</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2071</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4503</v>
+        <v>-0.1062</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7854</v>
+        <v>-1.5816</v>
       </c>
       <c r="F19" t="n">
-        <v>1.335</v>
+        <v>1.4754</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4412</v>
@@ -1936,13 +1936,13 @@
         <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0003</v>
+        <v>-0.6561</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0608</v>
+        <v>-0.857</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0605</v>
+        <v>0.2009</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4126</v>
+        <v>-1.174</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7876</v>
+        <v>-1.1359</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3749</v>
+        <v>-0.0381</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0581</v>
+        <v>0.2977</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.627</v>
+        <v>0.4719</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4311</v>
+        <v>-0.1742</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.948</v>
+        <v>1.4057</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3701</v>
+        <v>2.0045</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3181</v>
+        <v>-0.5988</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1101</v>
+        <v>-1.108</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9971</v>
+        <v>-1.5326</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.113</v>
+        <v>0.4246</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0859</v>
+        <v>-0.4102</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3816</v>
+        <v>-0.489</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2957</v>
+        <v>0.0788</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5331</v>
+        <v>-0.0704</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5331</v>
+        <v>-0.0704</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7644</v>
+        <v>-1.3217</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3566</v>
+        <v>-0.7454</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4078</v>
+        <v>-0.5763</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2723</v>
@@ -2092,13 +2092,13 @@
         <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8025</v>
+        <v>-0.3597</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9984</v>
+        <v>-0.3871</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1959</v>
+        <v>0.0274</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4737</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8753</v>
+        <v>-1.525</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6453</v>
+        <v>-1.7876</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2301</v>
+        <v>0.2626</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2977</v>
+        <v>-2.0581</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4719</v>
+        <v>-0.627</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1742</v>
+        <v>-1.4311</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4057</v>
+        <v>-0.948</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0045</v>
+        <v>0.3701</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5988</v>
+        <v>-1.3181</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.108</v>
+        <v>-1.1101</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5326</v>
+        <v>-0.9971</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4246</v>
+        <v>-0.113</v>
       </c>
       <c r="P22" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.9822</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1116</v>
+        <v>-0.1982</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9984</v>
+        <v>-0.3816</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1132</v>
+        <v>0.1834</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.0704</v>
+        <v>0.5331</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0704</v>
+        <v>0.5331</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9908</v>
+        <v>-3.4371</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5174</v>
+        <v>-2.2118</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4734</v>
+        <v>-1.2253</v>
       </c>
       <c r="G23" t="n">
         <v>0.5634</v>
@@ -2248,13 +2248,13 @@
         <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7019</v>
+        <v>-1.1481</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.6304</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7659</v>
+        <v>-0.5178</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8701</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7636</v>
+        <v>-5.9914</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9143</v>
+        <v>-4.6087</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-1.3828</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4431</v>
@@ -2326,13 +2326,13 @@
         <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0806</v>
+        <v>-0.3085</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8112</v>
+        <v>-0.5056</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7306</v>
+        <v>0.1971</v>
       </c>
       <c r="V24" t="n">
         <v>0.337</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.962700000000001</v>
+        <v>-3.2837</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8977</v>
+        <v>-1.897500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0654</v>
+        <v>-1.3864</v>
       </c>
       <c r="G25" t="n">
         <v>-1.281699999999999</v>
@@ -2374,7 +2374,7 @@
         <v>-1.3386</v>
       </c>
       <c r="I25" t="n">
-        <v>0.05690000000000039</v>
+        <v>0.05689999999999973</v>
       </c>
       <c r="J25" t="n">
         <v>7.053100000000001</v>
@@ -2383,7 +2383,7 @@
         <v>9.2332</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.180099999999999</v>
+        <v>-2.1801</v>
       </c>
       <c r="M25" t="n">
         <v>-8.3347</v>
@@ -2395,7 +2395,7 @@
         <v>2.2371</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9911999999999992</v>
+        <v>0.9912000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.8843</v>
@@ -2404,19 +2404,19 @@
         <v>13.8755</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.809200000000001</v>
+        <v>-4.1299</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.6971</v>
+        <v>-4.697000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.112</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>1.1368</v>
       </c>
       <c r="W25" t="n">
-        <v>8.630800000000001</v>
+        <v>8.630799999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-7.4941</v>
